--- a/output/version3/test/10-5/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="C2" t="n">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="D2" t="n">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="E2" t="n">
-        <v>595</v>
+        <v>467</v>
       </c>
       <c r="F2" t="n">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="G2" t="n">
-        <v>495</v>
+        <v>423</v>
       </c>
       <c r="H2" t="n">
-        <v>577</v>
+        <v>483</v>
       </c>
       <c r="I2" t="n">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="J2" t="n">
-        <v>552</v>
+        <v>467</v>
       </c>
       <c r="K2" t="n">
-        <v>491</v>
+        <v>519</v>
       </c>
       <c r="L2" t="n">
-        <v>520.3</v>
+        <v>477.3</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>600</v>
+        <v>494</v>
       </c>
       <c r="C3" t="n">
-        <v>584</v>
+        <v>543</v>
       </c>
       <c r="D3" t="n">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E3" t="n">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="F3" t="n">
-        <v>641</v>
+        <v>518</v>
       </c>
       <c r="G3" t="n">
-        <v>541</v>
+        <v>510</v>
       </c>
       <c r="H3" t="n">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="I3" t="n">
-        <v>529</v>
+        <v>484</v>
       </c>
       <c r="J3" t="n">
-        <v>610</v>
+        <v>560</v>
       </c>
       <c r="K3" t="n">
-        <v>577</v>
+        <v>514</v>
       </c>
       <c r="L3" t="n">
-        <v>572.2</v>
+        <v>526.6</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>591</v>
+        <v>504</v>
       </c>
       <c r="C4" t="n">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D4" t="n">
-        <v>573</v>
+        <v>532</v>
       </c>
       <c r="E4" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F4" t="n">
-        <v>552</v>
+        <v>465</v>
       </c>
       <c r="G4" t="n">
-        <v>549</v>
+        <v>495</v>
       </c>
       <c r="H4" t="n">
-        <v>594</v>
+        <v>511</v>
       </c>
       <c r="I4" t="n">
-        <v>586</v>
+        <v>504</v>
       </c>
       <c r="J4" t="n">
-        <v>538</v>
+        <v>442</v>
       </c>
       <c r="K4" t="n">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="L4" t="n">
-        <v>566.1</v>
+        <v>512.7</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C5" t="n">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="D5" t="n">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="E5" t="n">
-        <v>502</v>
+        <v>456</v>
       </c>
       <c r="F5" t="n">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="G5" t="n">
-        <v>544</v>
+        <v>473</v>
       </c>
       <c r="H5" t="n">
-        <v>526</v>
+        <v>445</v>
       </c>
       <c r="I5" t="n">
-        <v>522</v>
+        <v>445</v>
       </c>
       <c r="J5" t="n">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="K5" t="n">
-        <v>546</v>
+        <v>449</v>
       </c>
       <c r="L5" t="n">
-        <v>517.1</v>
+        <v>475.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>467</v>
+        <v>440</v>
       </c>
       <c r="C6" t="n">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="D6" t="n">
-        <v>553</v>
+        <v>463</v>
       </c>
       <c r="E6" t="n">
-        <v>509</v>
+        <v>437</v>
       </c>
       <c r="F6" t="n">
-        <v>499</v>
+        <v>447</v>
       </c>
       <c r="G6" t="n">
-        <v>520</v>
+        <v>445</v>
       </c>
       <c r="H6" t="n">
+        <v>507</v>
+      </c>
+      <c r="I6" t="n">
+        <v>487</v>
+      </c>
+      <c r="J6" t="n">
         <v>472</v>
       </c>
-      <c r="I6" t="n">
-        <v>557</v>
-      </c>
-      <c r="J6" t="n">
-        <v>527</v>
-      </c>
       <c r="K6" t="n">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="L6" t="n">
-        <v>510.3</v>
+        <v>474.3</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C7" t="n">
-        <v>599</v>
+        <v>413</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>440</v>
       </c>
       <c r="E7" t="n">
-        <v>537</v>
+        <v>433</v>
       </c>
       <c r="F7" t="n">
-        <v>456</v>
+        <v>516</v>
       </c>
       <c r="G7" t="n">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="H7" t="n">
-        <v>558</v>
+        <v>458</v>
       </c>
       <c r="I7" t="n">
-        <v>514</v>
+        <v>454</v>
       </c>
       <c r="J7" t="n">
-        <v>549</v>
+        <v>478</v>
       </c>
       <c r="K7" t="n">
-        <v>531</v>
+        <v>487</v>
       </c>
       <c r="L7" t="n">
-        <v>521.7</v>
+        <v>461.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="C8" t="n">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="D8" t="n">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="E8" t="n">
-        <v>574</v>
+        <v>486</v>
       </c>
       <c r="F8" t="n">
-        <v>491</v>
+        <v>544</v>
       </c>
       <c r="G8" t="n">
-        <v>494</v>
+        <v>536</v>
       </c>
       <c r="H8" t="n">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="I8" t="n">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="J8" t="n">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="K8" t="n">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="L8" t="n">
-        <v>519.6</v>
+        <v>520.6</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>457</v>
+        <v>501</v>
       </c>
       <c r="C9" t="n">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="D9" t="n">
-        <v>566</v>
+        <v>447</v>
       </c>
       <c r="E9" t="n">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="F9" t="n">
-        <v>535</v>
+        <v>469</v>
       </c>
       <c r="G9" t="n">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="H9" t="n">
-        <v>417</v>
+        <v>467</v>
       </c>
       <c r="I9" t="n">
-        <v>522</v>
+        <v>428</v>
       </c>
       <c r="J9" t="n">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="K9" t="n">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="L9" t="n">
-        <v>481.8</v>
+        <v>466.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
+        <v>462</v>
+      </c>
+      <c r="C10" t="n">
         <v>521</v>
       </c>
-      <c r="C10" t="n">
-        <v>502</v>
-      </c>
       <c r="D10" t="n">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="E10" t="n">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="F10" t="n">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="G10" t="n">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="H10" t="n">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="I10" t="n">
-        <v>489</v>
+        <v>579</v>
       </c>
       <c r="J10" t="n">
-        <v>559</v>
+        <v>491</v>
       </c>
       <c r="K10" t="n">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="L10" t="n">
-        <v>521.9</v>
+        <v>521.1</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>486</v>
+        <v>402</v>
       </c>
       <c r="C11" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D11" t="n">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="E11" t="n">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="F11" t="n">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G11" t="n">
-        <v>471</v>
+        <v>411</v>
       </c>
       <c r="H11" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I11" t="n">
-        <v>526</v>
+        <v>430</v>
       </c>
       <c r="J11" t="n">
-        <v>449</v>
+        <v>532</v>
       </c>
       <c r="K11" t="n">
-        <v>449</v>
+        <v>489</v>
       </c>
       <c r="L11" t="n">
-        <v>459.5</v>
+        <v>446.7</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>611</v>
+        <v>538</v>
       </c>
       <c r="C12" t="n">
-        <v>531</v>
+        <v>554</v>
       </c>
       <c r="D12" t="n">
-        <v>504</v>
+        <v>577</v>
       </c>
       <c r="E12" t="n">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="F12" t="n">
-        <v>644</v>
+        <v>524</v>
       </c>
       <c r="G12" t="n">
-        <v>607</v>
+        <v>510</v>
       </c>
       <c r="H12" t="n">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="I12" t="n">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="J12" t="n">
-        <v>555</v>
+        <v>589</v>
       </c>
       <c r="K12" t="n">
-        <v>615</v>
+        <v>545</v>
       </c>
       <c r="L12" t="n">
-        <v>572.4</v>
+        <v>553.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>529</v>
+        <v>492</v>
       </c>
       <c r="C13" t="n">
-        <v>662</v>
+        <v>552</v>
       </c>
       <c r="D13" t="n">
-        <v>430</v>
+        <v>580</v>
       </c>
       <c r="E13" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F13" t="n">
-        <v>576</v>
+        <v>502</v>
       </c>
       <c r="G13" t="n">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="H13" t="n">
-        <v>518</v>
+        <v>453</v>
       </c>
       <c r="I13" t="n">
-        <v>499</v>
+        <v>459</v>
       </c>
       <c r="J13" t="n">
-        <v>533</v>
+        <v>488</v>
       </c>
       <c r="K13" t="n">
-        <v>502</v>
+        <v>548</v>
       </c>
       <c r="L13" t="n">
-        <v>534.6</v>
+        <v>518.6</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>624</v>
+        <v>527</v>
       </c>
       <c r="C14" t="n">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D14" t="n">
-        <v>614</v>
+        <v>551</v>
       </c>
       <c r="E14" t="n">
-        <v>629</v>
+        <v>529</v>
       </c>
       <c r="F14" t="n">
-        <v>587</v>
+        <v>535</v>
       </c>
       <c r="G14" t="n">
-        <v>608</v>
+        <v>539</v>
       </c>
       <c r="H14" t="n">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="I14" t="n">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="J14" t="n">
-        <v>569</v>
+        <v>521</v>
       </c>
       <c r="K14" t="n">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="L14" t="n">
-        <v>584.8</v>
+        <v>547.2</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>597</v>
+        <v>517</v>
       </c>
       <c r="C15" t="n">
-        <v>564</v>
+        <v>448</v>
       </c>
       <c r="D15" t="n">
-        <v>545</v>
+        <v>487</v>
       </c>
       <c r="E15" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F15" t="n">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="G15" t="n">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="H15" t="n">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="I15" t="n">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="J15" t="n">
-        <v>636</v>
+        <v>489</v>
       </c>
       <c r="K15" t="n">
-        <v>597</v>
+        <v>518</v>
       </c>
       <c r="L15" t="n">
-        <v>554.5</v>
+        <v>500.3</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C16" t="n">
-        <v>553</v>
+        <v>466</v>
       </c>
       <c r="D16" t="n">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="E16" t="n">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="F16" t="n">
-        <v>451</v>
+        <v>521</v>
       </c>
       <c r="G16" t="n">
-        <v>565</v>
+        <v>464</v>
       </c>
       <c r="H16" t="n">
-        <v>570</v>
+        <v>513</v>
       </c>
       <c r="I16" t="n">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="J16" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K16" t="n">
-        <v>547</v>
+        <v>503</v>
       </c>
       <c r="L16" t="n">
-        <v>531.8</v>
+        <v>503.4</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="C17" t="n">
-        <v>565</v>
+        <v>538</v>
       </c>
       <c r="D17" t="n">
+        <v>470</v>
+      </c>
+      <c r="E17" t="n">
+        <v>433</v>
+      </c>
+      <c r="F17" t="n">
+        <v>495</v>
+      </c>
+      <c r="G17" t="n">
+        <v>457</v>
+      </c>
+      <c r="H17" t="n">
+        <v>491</v>
+      </c>
+      <c r="I17" t="n">
+        <v>440</v>
+      </c>
+      <c r="J17" t="n">
+        <v>467</v>
+      </c>
+      <c r="K17" t="n">
         <v>481</v>
       </c>
-      <c r="E17" t="n">
-        <v>548</v>
-      </c>
-      <c r="F17" t="n">
-        <v>449</v>
-      </c>
-      <c r="G17" t="n">
-        <v>579</v>
-      </c>
-      <c r="H17" t="n">
-        <v>528</v>
-      </c>
-      <c r="I17" t="n">
-        <v>583</v>
-      </c>
-      <c r="J17" t="n">
-        <v>495</v>
-      </c>
-      <c r="K17" t="n">
-        <v>536</v>
-      </c>
       <c r="L17" t="n">
-        <v>524</v>
+        <v>473.1</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>607</v>
+        <v>542</v>
       </c>
       <c r="C18" t="n">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D18" t="n">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="E18" t="n">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="F18" t="n">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="G18" t="n">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="H18" t="n">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="I18" t="n">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="J18" t="n">
-        <v>563</v>
+        <v>612</v>
       </c>
       <c r="K18" t="n">
-        <v>614</v>
+        <v>569</v>
       </c>
       <c r="L18" t="n">
-        <v>570.6</v>
+        <v>564.8</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>620</v>
+        <v>491</v>
       </c>
       <c r="C19" t="n">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="D19" t="n">
-        <v>578</v>
+        <v>508</v>
       </c>
       <c r="E19" t="n">
-        <v>629</v>
+        <v>457</v>
       </c>
       <c r="F19" t="n">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="G19" t="n">
-        <v>655</v>
+        <v>481</v>
       </c>
       <c r="H19" t="n">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="I19" t="n">
-        <v>496</v>
+        <v>567</v>
       </c>
       <c r="J19" t="n">
-        <v>560</v>
+        <v>506</v>
       </c>
       <c r="K19" t="n">
-        <v>581</v>
+        <v>518</v>
       </c>
       <c r="L19" t="n">
-        <v>566.1</v>
+        <v>512.7</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>513</v>
+        <v>580</v>
       </c>
       <c r="C20" t="n">
-        <v>585</v>
+        <v>497</v>
       </c>
       <c r="D20" t="n">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="E20" t="n">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="F20" t="n">
-        <v>629</v>
+        <v>511</v>
       </c>
       <c r="G20" t="n">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="H20" t="n">
-        <v>618</v>
+        <v>565</v>
       </c>
       <c r="I20" t="n">
-        <v>527</v>
+        <v>567</v>
       </c>
       <c r="J20" t="n">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="K20" t="n">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="L20" t="n">
-        <v>551.4</v>
+        <v>534.2</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C21" t="n">
-        <v>446</v>
+        <v>529</v>
       </c>
       <c r="D21" t="n">
-        <v>538</v>
+        <v>440</v>
       </c>
       <c r="E21" t="n">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F21" t="n">
-        <v>481</v>
+        <v>546</v>
       </c>
       <c r="G21" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="H21" t="n">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="I21" t="n">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="J21" t="n">
-        <v>522</v>
+        <v>480</v>
       </c>
       <c r="K21" t="n">
-        <v>582</v>
+        <v>477</v>
       </c>
       <c r="L21" t="n">
-        <v>503.5</v>
+        <v>481.9</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>501</v>
+        <v>538</v>
       </c>
       <c r="C22" t="n">
+        <v>493</v>
+      </c>
+      <c r="D22" t="n">
+        <v>558</v>
+      </c>
+      <c r="E22" t="n">
+        <v>507</v>
+      </c>
+      <c r="F22" t="n">
         <v>527</v>
       </c>
-      <c r="D22" t="n">
-        <v>518</v>
-      </c>
-      <c r="E22" t="n">
-        <v>485</v>
-      </c>
-      <c r="F22" t="n">
-        <v>618</v>
-      </c>
       <c r="G22" t="n">
-        <v>427</v>
+        <v>506</v>
       </c>
       <c r="H22" t="n">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="I22" t="n">
-        <v>573</v>
+        <v>480</v>
       </c>
       <c r="J22" t="n">
-        <v>539</v>
+        <v>503</v>
       </c>
       <c r="K22" t="n">
-        <v>562</v>
+        <v>466</v>
       </c>
       <c r="L22" t="n">
-        <v>522.8</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C23" t="n">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="D23" t="n">
-        <v>485</v>
+        <v>382</v>
       </c>
       <c r="E23" t="n">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="F23" t="n">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="G23" t="n">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="H23" t="n">
+        <v>412</v>
+      </c>
+      <c r="I23" t="n">
+        <v>465</v>
+      </c>
+      <c r="J23" t="n">
+        <v>476</v>
+      </c>
+      <c r="K23" t="n">
         <v>456</v>
       </c>
-      <c r="I23" t="n">
-        <v>462</v>
-      </c>
-      <c r="J23" t="n">
-        <v>414</v>
-      </c>
-      <c r="K23" t="n">
-        <v>400</v>
-      </c>
       <c r="L23" t="n">
-        <v>449.9</v>
+        <v>441.1</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="C24" t="n">
-        <v>434</v>
+        <v>473</v>
       </c>
       <c r="D24" t="n">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="E24" t="n">
-        <v>515</v>
+        <v>481</v>
       </c>
       <c r="F24" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="G24" t="n">
-        <v>438</v>
+        <v>483</v>
       </c>
       <c r="H24" t="n">
-        <v>555</v>
+        <v>397</v>
       </c>
       <c r="I24" t="n">
-        <v>532</v>
+        <v>477</v>
       </c>
       <c r="J24" t="n">
         <v>491</v>
       </c>
       <c r="K24" t="n">
-        <v>484</v>
+        <v>583</v>
       </c>
       <c r="L24" t="n">
-        <v>485.8</v>
+        <v>480.4</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="C25" t="n">
-        <v>533</v>
+        <v>442</v>
       </c>
       <c r="D25" t="n">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="E25" t="n">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="F25" t="n">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="G25" t="n">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="H25" t="n">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="I25" t="n">
-        <v>472</v>
+        <v>397</v>
       </c>
       <c r="J25" t="n">
-        <v>378</v>
+        <v>446</v>
       </c>
       <c r="K25" t="n">
-        <v>435</v>
+        <v>515</v>
       </c>
       <c r="L25" t="n">
-        <v>452.8</v>
+        <v>449.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>628</v>
+        <v>521</v>
       </c>
       <c r="C26" t="n">
-        <v>592</v>
+        <v>674</v>
       </c>
       <c r="D26" t="n">
-        <v>574</v>
+        <v>620</v>
       </c>
       <c r="E26" t="n">
-        <v>598</v>
+        <v>534</v>
       </c>
       <c r="F26" t="n">
-        <v>628</v>
+        <v>588</v>
       </c>
       <c r="G26" t="n">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="H26" t="n">
-        <v>684</v>
+        <v>610</v>
       </c>
       <c r="I26" t="n">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="J26" t="n">
-        <v>550</v>
+        <v>625</v>
       </c>
       <c r="K26" t="n">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="L26" t="n">
-        <v>598.1</v>
+        <v>594.7</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C27" t="n">
+        <v>438</v>
+      </c>
+      <c r="D27" t="n">
+        <v>446</v>
+      </c>
+      <c r="E27" t="n">
+        <v>463</v>
+      </c>
+      <c r="F27" t="n">
+        <v>436</v>
+      </c>
+      <c r="G27" t="n">
         <v>420</v>
       </c>
-      <c r="D27" t="n">
-        <v>458</v>
-      </c>
-      <c r="E27" t="n">
-        <v>452</v>
-      </c>
-      <c r="F27" t="n">
-        <v>505</v>
-      </c>
-      <c r="G27" t="n">
-        <v>463</v>
-      </c>
       <c r="H27" t="n">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="I27" t="n">
-        <v>532</v>
+        <v>449</v>
       </c>
       <c r="J27" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K27" t="n">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="L27" t="n">
-        <v>462.7</v>
+        <v>445.8</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="C28" t="n">
+        <v>519</v>
+      </c>
+      <c r="D28" t="n">
+        <v>440</v>
+      </c>
+      <c r="E28" t="n">
+        <v>493</v>
+      </c>
+      <c r="F28" t="n">
+        <v>449</v>
+      </c>
+      <c r="G28" t="n">
+        <v>494</v>
+      </c>
+      <c r="H28" t="n">
         <v>508</v>
       </c>
-      <c r="D28" t="n">
-        <v>509</v>
-      </c>
-      <c r="E28" t="n">
-        <v>520</v>
-      </c>
-      <c r="F28" t="n">
-        <v>556</v>
-      </c>
-      <c r="G28" t="n">
-        <v>523</v>
-      </c>
-      <c r="H28" t="n">
-        <v>512</v>
-      </c>
       <c r="I28" t="n">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="J28" t="n">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="K28" t="n">
-        <v>540</v>
+        <v>484</v>
       </c>
       <c r="L28" t="n">
-        <v>513.9</v>
+        <v>480.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C29" t="n">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="D29" t="n">
-        <v>472</v>
+        <v>434</v>
       </c>
       <c r="E29" t="n">
-        <v>511</v>
+        <v>437</v>
       </c>
       <c r="F29" t="n">
-        <v>472</v>
+        <v>433</v>
       </c>
       <c r="G29" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H29" t="n">
-        <v>500</v>
+        <v>416</v>
       </c>
       <c r="I29" t="n">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="J29" t="n">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="K29" t="n">
-        <v>491</v>
+        <v>421</v>
       </c>
       <c r="L29" t="n">
-        <v>477.8</v>
+        <v>441.4</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>536</v>
+        <v>410</v>
       </c>
       <c r="C30" t="n">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D30" t="n">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E30" t="n">
-        <v>579</v>
+        <v>489</v>
       </c>
       <c r="F30" t="n">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="G30" t="n">
-        <v>507</v>
+        <v>457</v>
       </c>
       <c r="H30" t="n">
-        <v>596</v>
+        <v>465</v>
       </c>
       <c r="I30" t="n">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="J30" t="n">
-        <v>594</v>
+        <v>419</v>
       </c>
       <c r="K30" t="n">
-        <v>532</v>
+        <v>464</v>
       </c>
       <c r="L30" t="n">
-        <v>522.8</v>
+        <v>464.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
+        <v>495</v>
+      </c>
+      <c r="C31" t="n">
+        <v>474</v>
+      </c>
+      <c r="D31" t="n">
+        <v>438</v>
+      </c>
+      <c r="E31" t="n">
         <v>505</v>
       </c>
-      <c r="C31" t="n">
-        <v>428</v>
-      </c>
-      <c r="D31" t="n">
-        <v>462</v>
-      </c>
-      <c r="E31" t="n">
-        <v>501</v>
-      </c>
       <c r="F31" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G31" t="n">
-        <v>466</v>
+        <v>526</v>
       </c>
       <c r="H31" t="n">
-        <v>525</v>
+        <v>491</v>
       </c>
       <c r="I31" t="n">
-        <v>442</v>
+        <v>534</v>
       </c>
       <c r="J31" t="n">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="K31" t="n">
-        <v>513</v>
+        <v>469</v>
       </c>
       <c r="L31" t="n">
-        <v>474.4</v>
+        <v>487</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="C32" t="n">
-        <v>553</v>
+        <v>430</v>
       </c>
       <c r="D32" t="n">
-        <v>490</v>
+        <v>413</v>
       </c>
       <c r="E32" t="n">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="F32" t="n">
-        <v>478</v>
+        <v>416</v>
       </c>
       <c r="G32" t="n">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="H32" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I32" t="n">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="J32" t="n">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="K32" t="n">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="L32" t="n">
-        <v>486.2</v>
+        <v>441.2</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="C33" t="n">
-        <v>441</v>
+        <v>481</v>
       </c>
       <c r="D33" t="n">
-        <v>455</v>
+        <v>396</v>
       </c>
       <c r="E33" t="n">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="F33" t="n">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="G33" t="n">
-        <v>445</v>
+        <v>535</v>
       </c>
       <c r="H33" t="n">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="I33" t="n">
-        <v>462</v>
+        <v>399</v>
       </c>
       <c r="J33" t="n">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K33" t="n">
-        <v>492</v>
+        <v>434</v>
       </c>
       <c r="L33" t="n">
-        <v>476.9</v>
+        <v>474.7</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>530</v>
+        <v>464</v>
       </c>
       <c r="C34" t="n">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D34" t="n">
-        <v>432</v>
+        <v>535</v>
       </c>
       <c r="E34" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F34" t="n">
-        <v>402</v>
+        <v>441</v>
       </c>
       <c r="G34" t="n">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="H34" t="n">
-        <v>437</v>
+        <v>477</v>
       </c>
       <c r="I34" t="n">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="J34" t="n">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="K34" t="n">
-        <v>541</v>
+        <v>477</v>
       </c>
       <c r="L34" t="n">
-        <v>473.4</v>
+        <v>477.5</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>559</v>
+        <v>466</v>
       </c>
       <c r="C35" t="n">
-        <v>535</v>
+        <v>441</v>
       </c>
       <c r="D35" t="n">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="E35" t="n">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="F35" t="n">
-        <v>537</v>
+        <v>501</v>
       </c>
       <c r="G35" t="n">
-        <v>422</v>
+        <v>525</v>
       </c>
       <c r="H35" t="n">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="I35" t="n">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="J35" t="n">
-        <v>655</v>
+        <v>520</v>
       </c>
       <c r="K35" t="n">
-        <v>475</v>
+        <v>520</v>
       </c>
       <c r="L35" t="n">
-        <v>526.1</v>
+        <v>511.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="C36" t="n">
-        <v>443</v>
+        <v>371</v>
       </c>
       <c r="D36" t="n">
-        <v>451</v>
+        <v>377</v>
       </c>
       <c r="E36" t="n">
-        <v>423</v>
+        <v>366</v>
       </c>
       <c r="F36" t="n">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="G36" t="n">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="H36" t="n">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="I36" t="n">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="J36" t="n">
         <v>389</v>
       </c>
       <c r="K36" t="n">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="L36" t="n">
-        <v>422.2</v>
+        <v>387.1</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="C37" t="n">
-        <v>521</v>
+        <v>453</v>
       </c>
       <c r="D37" t="n">
-        <v>492</v>
+        <v>576</v>
       </c>
       <c r="E37" t="n">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="F37" t="n">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="G37" t="n">
-        <v>579</v>
+        <v>510</v>
       </c>
       <c r="H37" t="n">
-        <v>582</v>
+        <v>514</v>
       </c>
       <c r="I37" t="n">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="J37" t="n">
-        <v>605</v>
+        <v>516</v>
       </c>
       <c r="K37" t="n">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="L37" t="n">
-        <v>528.7</v>
+        <v>493.6</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C38" t="n">
-        <v>646</v>
+        <v>572</v>
       </c>
       <c r="D38" t="n">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="E38" t="n">
-        <v>693</v>
+        <v>652</v>
       </c>
       <c r="F38" t="n">
-        <v>577</v>
+        <v>619</v>
       </c>
       <c r="G38" t="n">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="H38" t="n">
-        <v>626</v>
+        <v>483</v>
       </c>
       <c r="I38" t="n">
-        <v>626</v>
+        <v>562</v>
       </c>
       <c r="J38" t="n">
-        <v>609</v>
+        <v>549</v>
       </c>
       <c r="K38" t="n">
-        <v>624</v>
+        <v>545</v>
       </c>
       <c r="L38" t="n">
-        <v>625.6</v>
+        <v>587</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="C39" t="n">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="D39" t="n">
-        <v>590</v>
+        <v>402</v>
       </c>
       <c r="E39" t="n">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="F39" t="n">
-        <v>446</v>
+        <v>381</v>
       </c>
       <c r="G39" t="n">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="H39" t="n">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="I39" t="n">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="J39" t="n">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="K39" t="n">
-        <v>500</v>
+        <v>416</v>
       </c>
       <c r="L39" t="n">
-        <v>483</v>
+        <v>446.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>539</v>
+        <v>446</v>
       </c>
       <c r="C40" t="n">
-        <v>521</v>
+        <v>466</v>
       </c>
       <c r="D40" t="n">
+        <v>467</v>
+      </c>
+      <c r="E40" t="n">
+        <v>462</v>
+      </c>
+      <c r="F40" t="n">
+        <v>457</v>
+      </c>
+      <c r="G40" t="n">
+        <v>462</v>
+      </c>
+      <c r="H40" t="n">
+        <v>487</v>
+      </c>
+      <c r="I40" t="n">
+        <v>499</v>
+      </c>
+      <c r="J40" t="n">
         <v>491</v>
       </c>
-      <c r="E40" t="n">
-        <v>556</v>
-      </c>
-      <c r="F40" t="n">
-        <v>490</v>
-      </c>
-      <c r="G40" t="n">
-        <v>539</v>
-      </c>
-      <c r="H40" t="n">
-        <v>539</v>
-      </c>
-      <c r="I40" t="n">
-        <v>527</v>
-      </c>
-      <c r="J40" t="n">
-        <v>550</v>
-      </c>
       <c r="K40" t="n">
-        <v>528</v>
+        <v>429</v>
       </c>
       <c r="L40" t="n">
-        <v>528</v>
+        <v>466.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="C41" t="n">
-        <v>578</v>
+        <v>547</v>
       </c>
       <c r="D41" t="n">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E41" t="n">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="F41" t="n">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="G41" t="n">
-        <v>487</v>
+        <v>596</v>
       </c>
       <c r="H41" t="n">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="I41" t="n">
-        <v>451</v>
+        <v>535</v>
       </c>
       <c r="J41" t="n">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="K41" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="L41" t="n">
-        <v>526.8</v>
+        <v>543.7</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>542</v>
+        <v>511</v>
       </c>
       <c r="C42" t="n">
-        <v>431</v>
+        <v>499</v>
       </c>
       <c r="D42" t="n">
-        <v>509</v>
+        <v>430</v>
       </c>
       <c r="E42" t="n">
-        <v>524</v>
+        <v>457</v>
       </c>
       <c r="F42" t="n">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="G42" t="n">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="H42" t="n">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="I42" t="n">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="J42" t="n">
-        <v>441</v>
+        <v>537</v>
       </c>
       <c r="K42" t="n">
-        <v>502</v>
+        <v>406</v>
       </c>
       <c r="L42" t="n">
-        <v>490.8</v>
+        <v>475.2</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>461</v>
+        <v>540</v>
       </c>
       <c r="C43" t="n">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D43" t="n">
-        <v>556</v>
+        <v>505</v>
       </c>
       <c r="E43" t="n">
-        <v>448</v>
+        <v>595</v>
       </c>
       <c r="F43" t="n">
-        <v>600</v>
+        <v>491</v>
       </c>
       <c r="G43" t="n">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="H43" t="n">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="I43" t="n">
-        <v>505</v>
+        <v>592</v>
       </c>
       <c r="J43" t="n">
-        <v>473</v>
+        <v>536</v>
       </c>
       <c r="K43" t="n">
-        <v>507</v>
+        <v>560</v>
       </c>
       <c r="L43" t="n">
-        <v>505.1</v>
+        <v>532</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="C44" t="n">
-        <v>479</v>
+        <v>528</v>
       </c>
       <c r="D44" t="n">
-        <v>608</v>
+        <v>515</v>
       </c>
       <c r="E44" t="n">
-        <v>450</v>
+        <v>491</v>
       </c>
       <c r="F44" t="n">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="G44" t="n">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="H44" t="n">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="I44" t="n">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="J44" t="n">
         <v>460</v>
       </c>
       <c r="K44" t="n">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="L44" t="n">
-        <v>505.9</v>
+        <v>496.8</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>478</v>
+        <v>513</v>
       </c>
       <c r="C45" t="n">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="D45" t="n">
-        <v>429</v>
+        <v>520</v>
       </c>
       <c r="E45" t="n">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="F45" t="n">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="G45" t="n">
-        <v>462</v>
+        <v>497</v>
       </c>
       <c r="H45" t="n">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="I45" t="n">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="J45" t="n">
-        <v>552</v>
+        <v>422</v>
       </c>
       <c r="K45" t="n">
-        <v>565</v>
+        <v>489</v>
       </c>
       <c r="L45" t="n">
-        <v>487.8</v>
+        <v>488.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="C46" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D46" t="n">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="E46" t="n">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="F46" t="n">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="G46" t="n">
-        <v>466</v>
+        <v>522</v>
       </c>
       <c r="H46" t="n">
-        <v>579</v>
+        <v>447</v>
       </c>
       <c r="I46" t="n">
-        <v>494</v>
+        <v>397</v>
       </c>
       <c r="J46" t="n">
-        <v>522</v>
+        <v>429</v>
       </c>
       <c r="K46" t="n">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="L46" t="n">
-        <v>455</v>
+        <v>433.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>625</v>
+        <v>573</v>
       </c>
       <c r="C47" t="n">
-        <v>553</v>
+        <v>645</v>
       </c>
       <c r="D47" t="n">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="E47" t="n">
-        <v>548</v>
+        <v>600</v>
       </c>
       <c r="F47" t="n">
-        <v>589</v>
+        <v>538</v>
       </c>
       <c r="G47" t="n">
-        <v>567</v>
+        <v>502</v>
       </c>
       <c r="H47" t="n">
-        <v>596</v>
+        <v>571</v>
       </c>
       <c r="I47" t="n">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="J47" t="n">
-        <v>532</v>
+        <v>580</v>
       </c>
       <c r="K47" t="n">
-        <v>585</v>
+        <v>525</v>
       </c>
       <c r="L47" t="n">
-        <v>570.9</v>
+        <v>564</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>617</v>
+        <v>560</v>
       </c>
       <c r="C48" t="n">
-        <v>611</v>
+        <v>493</v>
       </c>
       <c r="D48" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E48" t="n">
-        <v>568</v>
+        <v>530</v>
       </c>
       <c r="F48" t="n">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="G48" t="n">
-        <v>582</v>
+        <v>499</v>
       </c>
       <c r="H48" t="n">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="I48" t="n">
-        <v>580</v>
+        <v>529</v>
       </c>
       <c r="J48" t="n">
-        <v>625</v>
+        <v>594</v>
       </c>
       <c r="K48" t="n">
-        <v>594</v>
+        <v>540</v>
       </c>
       <c r="L48" t="n">
-        <v>578.3</v>
+        <v>526.3</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>521</v>
+        <v>481</v>
       </c>
       <c r="C49" t="n">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="D49" t="n">
-        <v>507</v>
+        <v>428</v>
       </c>
       <c r="E49" t="n">
-        <v>557</v>
+        <v>422</v>
       </c>
       <c r="F49" t="n">
-        <v>532</v>
+        <v>560</v>
       </c>
       <c r="G49" t="n">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="H49" t="n">
-        <v>467</v>
+        <v>512</v>
       </c>
       <c r="I49" t="n">
-        <v>507</v>
+        <v>458</v>
       </c>
       <c r="J49" t="n">
-        <v>483</v>
+        <v>524</v>
       </c>
       <c r="K49" t="n">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="L49" t="n">
-        <v>497.9</v>
+        <v>481.3</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C50" t="n">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D50" t="n">
+        <v>524</v>
+      </c>
+      <c r="E50" t="n">
+        <v>517</v>
+      </c>
+      <c r="F50" t="n">
         <v>506</v>
       </c>
-      <c r="E50" t="n">
-        <v>559</v>
-      </c>
-      <c r="F50" t="n">
-        <v>528</v>
-      </c>
       <c r="G50" t="n">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="H50" t="n">
-        <v>574</v>
+        <v>470</v>
       </c>
       <c r="I50" t="n">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="J50" t="n">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="K50" t="n">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="L50" t="n">
-        <v>513.1</v>
+        <v>504.2</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
+        <v>493</v>
+      </c>
+      <c r="C51" t="n">
         <v>461</v>
       </c>
-      <c r="C51" t="n">
-        <v>504</v>
-      </c>
       <c r="D51" t="n">
-        <v>511</v>
+        <v>444</v>
       </c>
       <c r="E51" t="n">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="F51" t="n">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="G51" t="n">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="H51" t="n">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="I51" t="n">
-        <v>462</v>
+        <v>423</v>
       </c>
       <c r="J51" t="n">
-        <v>502</v>
+        <v>452</v>
       </c>
       <c r="K51" t="n">
-        <v>445</v>
+        <v>555</v>
       </c>
       <c r="L51" t="n">
-        <v>479.6</v>
+        <v>471.6</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>516.62</v>
+        <v>485.04</v>
       </c>
       <c r="C52" t="n">
-        <v>514.16</v>
+        <v>495.18</v>
       </c>
       <c r="D52" t="n">
-        <v>509.22</v>
+        <v>488.92</v>
       </c>
       <c r="E52" t="n">
-        <v>525.22</v>
+        <v>495.88</v>
       </c>
       <c r="F52" t="n">
-        <v>515</v>
+        <v>496.28</v>
       </c>
       <c r="G52" t="n">
-        <v>509.64</v>
+        <v>493.98</v>
       </c>
       <c r="H52" t="n">
-        <v>521</v>
+        <v>492.96</v>
       </c>
       <c r="I52" t="n">
-        <v>507.98</v>
+        <v>486.46</v>
       </c>
       <c r="J52" t="n">
-        <v>522.0599999999999</v>
+        <v>499.06</v>
       </c>
       <c r="K52" t="n">
-        <v>520.4</v>
+        <v>499.16</v>
       </c>
       <c r="L52" t="n">
-        <v>516.1299999999999</v>
+        <v>493.292</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.469565868377686</v>
+        <v>2.261669397354126</v>
       </c>
       <c r="C2" t="n">
-        <v>2.291348218917847</v>
+        <v>2.387794256210327</v>
       </c>
       <c r="D2" t="n">
-        <v>2.364426612854004</v>
+        <v>2.552201986312866</v>
       </c>
       <c r="E2" t="n">
-        <v>2.440452098846436</v>
+        <v>2.729598760604858</v>
       </c>
       <c r="F2" t="n">
-        <v>2.140557527542114</v>
+        <v>2.564507007598877</v>
       </c>
       <c r="G2" t="n">
-        <v>2.569998741149902</v>
+        <v>2.423850536346436</v>
       </c>
       <c r="H2" t="n">
-        <v>2.540711402893066</v>
+        <v>2.585459232330322</v>
       </c>
       <c r="I2" t="n">
-        <v>3.275758981704712</v>
+        <v>2.650829792022705</v>
       </c>
       <c r="J2" t="n">
-        <v>3.314558267593384</v>
+        <v>2.01685619354248</v>
       </c>
       <c r="K2" t="n">
-        <v>2.307621717453003</v>
+        <v>2.243287324905396</v>
       </c>
       <c r="L2" t="n">
-        <v>2.571499943733215</v>
+        <v>2.441605448722839</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.524057626724243</v>
+        <v>2.364818811416626</v>
       </c>
       <c r="C3" t="n">
-        <v>2.493135929107666</v>
+        <v>2.577841758728027</v>
       </c>
       <c r="D3" t="n">
-        <v>2.432803153991699</v>
+        <v>2.518496513366699</v>
       </c>
       <c r="E3" t="n">
-        <v>2.446774244308472</v>
+        <v>3.080024242401123</v>
       </c>
       <c r="F3" t="n">
-        <v>2.46024227142334</v>
+        <v>2.50299596786499</v>
       </c>
       <c r="G3" t="n">
-        <v>2.304650068283081</v>
+        <v>2.263956308364868</v>
       </c>
       <c r="H3" t="n">
-        <v>2.178445100784302</v>
+        <v>2.475221872329712</v>
       </c>
       <c r="I3" t="n">
-        <v>2.325579881668091</v>
+        <v>2.247259855270386</v>
       </c>
       <c r="J3" t="n">
-        <v>2.635267019271851</v>
+        <v>2.723962783813477</v>
       </c>
       <c r="K3" t="n">
-        <v>2.498124361038208</v>
+        <v>2.248674392700195</v>
       </c>
       <c r="L3" t="n">
-        <v>2.429907965660095</v>
+        <v>2.50032525062561</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.950525045394897</v>
+        <v>2.338446855545044</v>
       </c>
       <c r="C4" t="n">
-        <v>2.996711015701294</v>
+        <v>2.61719799041748</v>
       </c>
       <c r="D4" t="n">
-        <v>2.305624008178711</v>
+        <v>2.503998279571533</v>
       </c>
       <c r="E4" t="n">
-        <v>2.410858869552612</v>
+        <v>2.434693098068237</v>
       </c>
       <c r="F4" t="n">
-        <v>3.810061693191528</v>
+        <v>2.38963508605957</v>
       </c>
       <c r="G4" t="n">
-        <v>3.361876964569092</v>
+        <v>2.764888286590576</v>
       </c>
       <c r="H4" t="n">
-        <v>3.007625579833984</v>
+        <v>2.703491687774658</v>
       </c>
       <c r="I4" t="n">
-        <v>2.676539659500122</v>
+        <v>2.595286130905151</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96724534034729</v>
+        <v>2.266116380691528</v>
       </c>
       <c r="K4" t="n">
-        <v>2.750432014465332</v>
+        <v>2.378246545791626</v>
       </c>
       <c r="L4" t="n">
-        <v>2.923750019073486</v>
+        <v>2.49920003414154</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2.262228012084961</v>
+        <v>2.149537563323975</v>
       </c>
       <c r="C5" t="n">
-        <v>2.568223237991333</v>
+        <v>2.283039808273315</v>
       </c>
       <c r="D5" t="n">
-        <v>2.916489839553833</v>
+        <v>2.620886564254761</v>
       </c>
       <c r="E5" t="n">
-        <v>2.360801696777344</v>
+        <v>2.340581178665161</v>
       </c>
       <c r="F5" t="n">
-        <v>2.515425443649292</v>
+        <v>2.255285263061523</v>
       </c>
       <c r="G5" t="n">
-        <v>3.586944341659546</v>
+        <v>2.303653001785278</v>
       </c>
       <c r="H5" t="n">
-        <v>2.476672649383545</v>
+        <v>2.571483135223389</v>
       </c>
       <c r="I5" t="n">
-        <v>2.163492679595947</v>
+        <v>2.360069274902344</v>
       </c>
       <c r="J5" t="n">
-        <v>2.493151903152466</v>
+        <v>2.764493465423584</v>
       </c>
       <c r="K5" t="n">
-        <v>2.047791004180908</v>
+        <v>2.378974676132202</v>
       </c>
       <c r="L5" t="n">
-        <v>2.539122080802918</v>
+        <v>2.402800393104553</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1.964009284973145</v>
+        <v>1.864758968353271</v>
       </c>
       <c r="C6" t="n">
-        <v>1.989922285079956</v>
+        <v>2.156619787216187</v>
       </c>
       <c r="D6" t="n">
-        <v>2.228329658508301</v>
+        <v>2.149558544158936</v>
       </c>
       <c r="E6" t="n">
-        <v>1.911634206771851</v>
+        <v>2.335569143295288</v>
       </c>
       <c r="F6" t="n">
-        <v>1.871725797653198</v>
+        <v>2.065241813659668</v>
       </c>
       <c r="G6" t="n">
-        <v>2.097654819488525</v>
+        <v>1.918628692626953</v>
       </c>
       <c r="H6" t="n">
-        <v>1.90265417098999</v>
+        <v>2.049768686294556</v>
       </c>
       <c r="I6" t="n">
-        <v>2.232808828353882</v>
+        <v>2.069229602813721</v>
       </c>
       <c r="J6" t="n">
-        <v>1.99191951751709</v>
+        <v>1.948614120483398</v>
       </c>
       <c r="K6" t="n">
-        <v>1.867229223251343</v>
+        <v>2.095177888870239</v>
       </c>
       <c r="L6" t="n">
-        <v>2.005788779258728</v>
+        <v>2.065316724777222</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.332067251205444</v>
+        <v>2.083190679550171</v>
       </c>
       <c r="C7" t="n">
-        <v>2.479662656784058</v>
+        <v>2.386936664581299</v>
       </c>
       <c r="D7" t="n">
-        <v>2.41185736656189</v>
+        <v>2.220342636108398</v>
       </c>
       <c r="E7" t="n">
-        <v>2.475197553634644</v>
+        <v>2.249787092208862</v>
       </c>
       <c r="F7" t="n">
-        <v>2.35703444480896</v>
+        <v>2.385428190231323</v>
       </c>
       <c r="G7" t="n">
-        <v>2.288153648376465</v>
+        <v>2.128604412078857</v>
       </c>
       <c r="H7" t="n">
-        <v>2.401374578475952</v>
+        <v>2.29514479637146</v>
       </c>
       <c r="I7" t="n">
-        <v>3.562018871307373</v>
+        <v>2.153008222579956</v>
       </c>
       <c r="J7" t="n">
-        <v>2.295516967773438</v>
+        <v>2.508285760879517</v>
       </c>
       <c r="K7" t="n">
-        <v>2.315474033355713</v>
+        <v>2.224435567855835</v>
       </c>
       <c r="L7" t="n">
-        <v>2.491835737228393</v>
+        <v>2.263516402244568</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.283066987991333</v>
+        <v>2.140560865402222</v>
       </c>
       <c r="C8" t="n">
-        <v>2.498001098632812</v>
+        <v>2.389922142028809</v>
       </c>
       <c r="D8" t="n">
-        <v>2.218238830566406</v>
+        <v>2.032804250717163</v>
       </c>
       <c r="E8" t="n">
-        <v>2.28455662727356</v>
+        <v>2.890587568283081</v>
       </c>
       <c r="F8" t="n">
-        <v>2.216224670410156</v>
+        <v>2.353691101074219</v>
       </c>
       <c r="G8" t="n">
-        <v>2.370859622955322</v>
+        <v>2.262612581253052</v>
       </c>
       <c r="H8" t="n">
-        <v>2.282550573348999</v>
+        <v>2.495022535324097</v>
       </c>
       <c r="I8" t="n">
-        <v>2.432665824890137</v>
+        <v>2.159894943237305</v>
       </c>
       <c r="J8" t="n">
-        <v>2.405792951583862</v>
+        <v>2.318490505218506</v>
       </c>
       <c r="K8" t="n">
-        <v>2.266638040542603</v>
+        <v>2.255621671676636</v>
       </c>
       <c r="L8" t="n">
-        <v>2.325859522819519</v>
+        <v>2.329920816421509</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.181325912475586</v>
+        <v>2.273603916168213</v>
       </c>
       <c r="C9" t="n">
-        <v>2.135932683944702</v>
+        <v>2.376868724822998</v>
       </c>
       <c r="D9" t="n">
-        <v>2.262104988098145</v>
+        <v>2.301532030105591</v>
       </c>
       <c r="E9" t="n">
-        <v>2.241662502288818</v>
+        <v>2.346393823623657</v>
       </c>
       <c r="F9" t="n">
-        <v>2.371332406997681</v>
+        <v>2.258631706237793</v>
       </c>
       <c r="G9" t="n">
-        <v>2.085067272186279</v>
+        <v>2.294051647186279</v>
       </c>
       <c r="H9" t="n">
-        <v>2.18830680847168</v>
+        <v>2.211032390594482</v>
       </c>
       <c r="I9" t="n">
-        <v>2.332435369491577</v>
+        <v>2.151906728744507</v>
       </c>
       <c r="J9" t="n">
-        <v>2.079104661941528</v>
+        <v>2.261164665222168</v>
       </c>
       <c r="K9" t="n">
-        <v>2.359858512878418</v>
+        <v>2.069715023040771</v>
       </c>
       <c r="L9" t="n">
-        <v>2.223713111877442</v>
+        <v>2.254490065574646</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.413774490356445</v>
+        <v>2.115556001663208</v>
       </c>
       <c r="C10" t="n">
-        <v>2.347388029098511</v>
+        <v>2.111744165420532</v>
       </c>
       <c r="D10" t="n">
-        <v>2.250649690628052</v>
+        <v>2.165494441986084</v>
       </c>
       <c r="E10" t="n">
-        <v>2.191301107406616</v>
+        <v>2.134062528610229</v>
       </c>
       <c r="F10" t="n">
-        <v>2.225217819213867</v>
+        <v>2.239812612533569</v>
       </c>
       <c r="G10" t="n">
-        <v>2.185320854187012</v>
+        <v>2.324029922485352</v>
       </c>
       <c r="H10" t="n">
-        <v>2.296530961990356</v>
+        <v>2.285582065582275</v>
       </c>
       <c r="I10" t="n">
-        <v>2.143069267272949</v>
+        <v>2.545910358428955</v>
       </c>
       <c r="J10" t="n">
-        <v>2.223009347915649</v>
+        <v>2.113002061843872</v>
       </c>
       <c r="K10" t="n">
-        <v>2.154528617858887</v>
+        <v>2.312506437301636</v>
       </c>
       <c r="L10" t="n">
-        <v>2.243079018592835</v>
+        <v>2.234770059585571</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>2.266233444213867</v>
+        <v>1.854690790176392</v>
       </c>
       <c r="C11" t="n">
-        <v>1.985941648483276</v>
+        <v>1.908535957336426</v>
       </c>
       <c r="D11" t="n">
-        <v>1.961011648178101</v>
+        <v>1.847183704376221</v>
       </c>
       <c r="E11" t="n">
-        <v>1.90863299369812</v>
+        <v>1.873633146286011</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9475417137146</v>
+        <v>1.895561933517456</v>
       </c>
       <c r="G11" t="n">
-        <v>2.146537780761719</v>
+        <v>1.899576902389526</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1091628074646</v>
+        <v>2.009791851043701</v>
       </c>
       <c r="I11" t="n">
-        <v>2.051764726638794</v>
+        <v>1.864656209945679</v>
       </c>
       <c r="J11" t="n">
-        <v>2.046297788619995</v>
+        <v>1.986329078674316</v>
       </c>
       <c r="K11" t="n">
-        <v>1.989420413970947</v>
+        <v>1.944939613342285</v>
       </c>
       <c r="L11" t="n">
-        <v>2.041254496574402</v>
+        <v>1.908489918708801</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.384926557540894</v>
+        <v>2.151898145675659</v>
       </c>
       <c r="C12" t="n">
-        <v>2.076200246810913</v>
+        <v>2.345913648605347</v>
       </c>
       <c r="D12" t="n">
-        <v>2.094157934188843</v>
+        <v>2.346031188964844</v>
       </c>
       <c r="E12" t="n">
-        <v>2.12510347366333</v>
+        <v>2.307624340057373</v>
       </c>
       <c r="F12" t="n">
-        <v>2.434796571731567</v>
+        <v>2.063282012939453</v>
       </c>
       <c r="G12" t="n">
-        <v>2.160498380661011</v>
+        <v>2.09717583656311</v>
       </c>
       <c r="H12" t="n">
-        <v>2.396890163421631</v>
+        <v>2.225226163864136</v>
       </c>
       <c r="I12" t="n">
-        <v>2.255254983901978</v>
+        <v>2.003897905349731</v>
       </c>
       <c r="J12" t="n">
-        <v>2.200398683547974</v>
+        <v>2.075215101242065</v>
       </c>
       <c r="K12" t="n">
-        <v>2.48916482925415</v>
+        <v>2.14901328086853</v>
       </c>
       <c r="L12" t="n">
-        <v>2.261739182472229</v>
+        <v>2.176527762413025</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.203374147415161</v>
+        <v>2.137058973312378</v>
       </c>
       <c r="C13" t="n">
-        <v>2.480183124542236</v>
+        <v>2.391948938369751</v>
       </c>
       <c r="D13" t="n">
-        <v>2.022844076156616</v>
+        <v>2.156504392623901</v>
       </c>
       <c r="E13" t="n">
-        <v>2.144544839859009</v>
+        <v>2.383936405181885</v>
       </c>
       <c r="F13" t="n">
-        <v>2.315594673156738</v>
+        <v>2.136041402816772</v>
       </c>
       <c r="G13" t="n">
-        <v>2.240286111831665</v>
+        <v>2.466223478317261</v>
       </c>
       <c r="H13" t="n">
-        <v>2.297635555267334</v>
+        <v>2.149023532867432</v>
       </c>
       <c r="I13" t="n">
-        <v>2.151019096374512</v>
+        <v>2.37196159362793</v>
       </c>
       <c r="J13" t="n">
-        <v>2.214856863021851</v>
+        <v>2.193414688110352</v>
       </c>
       <c r="K13" t="n">
-        <v>2.096637964248657</v>
+        <v>2.267237901687622</v>
       </c>
       <c r="L13" t="n">
-        <v>2.216697645187378</v>
+        <v>2.265335130691528</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.564947128295898</v>
+        <v>2.300643920898438</v>
       </c>
       <c r="C14" t="n">
-        <v>2.185431003570557</v>
+        <v>2.1894211769104</v>
       </c>
       <c r="D14" t="n">
-        <v>2.307617664337158</v>
+        <v>2.312607526779175</v>
       </c>
       <c r="E14" t="n">
-        <v>2.360994100570679</v>
+        <v>2.245805740356445</v>
       </c>
       <c r="F14" t="n">
-        <v>2.388398408889771</v>
+        <v>2.127102613449097</v>
       </c>
       <c r="G14" t="n">
-        <v>2.247773170471191</v>
+        <v>2.289671421051025</v>
       </c>
       <c r="H14" t="n">
-        <v>2.332547426223755</v>
+        <v>2.452672481536865</v>
       </c>
       <c r="I14" t="n">
-        <v>2.180445909500122</v>
+        <v>2.309496402740479</v>
       </c>
       <c r="J14" t="n">
-        <v>2.30461859703064</v>
+        <v>2.335447311401367</v>
       </c>
       <c r="K14" t="n">
-        <v>2.336533546447754</v>
+        <v>2.481054782867432</v>
       </c>
       <c r="L14" t="n">
-        <v>2.320930695533753</v>
+        <v>2.304392337799072</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.155513286590576</v>
+        <v>2.145423889160156</v>
       </c>
       <c r="C15" t="n">
-        <v>2.173960208892822</v>
+        <v>1.909528732299805</v>
       </c>
       <c r="D15" t="n">
-        <v>2.344027519226074</v>
+        <v>2.185323238372803</v>
       </c>
       <c r="E15" t="n">
-        <v>2.517098188400269</v>
+        <v>2.078584671020508</v>
       </c>
       <c r="F15" t="n">
-        <v>2.304632186889648</v>
+        <v>2.07412314414978</v>
       </c>
       <c r="G15" t="n">
-        <v>2.151031970977783</v>
+        <v>2.04866361618042</v>
       </c>
       <c r="H15" t="n">
-        <v>2.188437700271606</v>
+        <v>1.999796152114868</v>
       </c>
       <c r="I15" t="n">
-        <v>2.163180112838745</v>
+        <v>2.239670038223267</v>
       </c>
       <c r="J15" t="n">
-        <v>2.291533470153809</v>
+        <v>2.096056222915649</v>
       </c>
       <c r="K15" t="n">
-        <v>2.265101432800293</v>
+        <v>2.030710458755493</v>
       </c>
       <c r="L15" t="n">
-        <v>2.255451607704162</v>
+        <v>2.080788016319275</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.217736005783081</v>
+        <v>2.026732921600342</v>
       </c>
       <c r="C16" t="n">
-        <v>2.407747268676758</v>
+        <v>2.094056844711304</v>
       </c>
       <c r="D16" t="n">
-        <v>2.523946285247803</v>
+        <v>2.139433622360229</v>
       </c>
       <c r="E16" t="n">
-        <v>2.377313137054443</v>
+        <v>2.288053274154663</v>
       </c>
       <c r="F16" t="n">
-        <v>2.159887552261353</v>
+        <v>2.193906307220459</v>
       </c>
       <c r="G16" t="n">
-        <v>2.424681663513184</v>
+        <v>2.126679658889771</v>
       </c>
       <c r="H16" t="n">
-        <v>2.354866981506348</v>
+        <v>2.103137254714966</v>
       </c>
       <c r="I16" t="n">
-        <v>2.103023529052734</v>
+        <v>2.081209182739258</v>
       </c>
       <c r="J16" t="n">
-        <v>2.245152950286865</v>
+        <v>2.279698848724365</v>
       </c>
       <c r="K16" t="n">
-        <v>2.100032091140747</v>
+        <v>2.084232330322266</v>
       </c>
       <c r="L16" t="n">
-        <v>2.291438746452331</v>
+        <v>2.141714024543762</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.130961656570435</v>
+        <v>2.151011228561401</v>
       </c>
       <c r="C17" t="n">
-        <v>2.384804248809814</v>
+        <v>2.097152948379517</v>
       </c>
       <c r="D17" t="n">
-        <v>2.233185291290283</v>
+        <v>2.327568769454956</v>
       </c>
       <c r="E17" t="n">
-        <v>2.130470275878906</v>
+        <v>2.099157810211182</v>
       </c>
       <c r="F17" t="n">
-        <v>2.015833377838135</v>
+        <v>2.118618249893188</v>
       </c>
       <c r="G17" t="n">
-        <v>2.162882089614868</v>
+        <v>2.058748245239258</v>
       </c>
       <c r="H17" t="n">
-        <v>2.450133323669434</v>
+        <v>2.124101877212524</v>
       </c>
       <c r="I17" t="n">
-        <v>2.032706260681152</v>
+        <v>2.13757848739624</v>
       </c>
       <c r="J17" t="n">
-        <v>2.219223976135254</v>
+        <v>2.058753967285156</v>
       </c>
       <c r="K17" t="n">
-        <v>2.723931074142456</v>
+        <v>2.222344875335693</v>
       </c>
       <c r="L17" t="n">
-        <v>2.248413157463074</v>
+        <v>2.139503645896911</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.660090923309326</v>
+        <v>2.386923551559448</v>
       </c>
       <c r="C18" t="n">
-        <v>2.379800796508789</v>
+        <v>2.363993644714355</v>
       </c>
       <c r="D18" t="n">
-        <v>2.403748512268066</v>
+        <v>2.385929822921753</v>
       </c>
       <c r="E18" t="n">
-        <v>2.450628519058228</v>
+        <v>2.328573226928711</v>
       </c>
       <c r="F18" t="n">
-        <v>2.658579587936401</v>
+        <v>2.590401649475098</v>
       </c>
       <c r="G18" t="n">
-        <v>2.446633577346802</v>
+        <v>2.411849498748779</v>
       </c>
       <c r="H18" t="n">
-        <v>2.429180383682251</v>
+        <v>2.41085958480835</v>
       </c>
       <c r="I18" t="n">
-        <v>2.573811292648315</v>
+        <v>2.476199150085449</v>
       </c>
       <c r="J18" t="n">
-        <v>2.544402599334717</v>
+        <v>2.495629549026489</v>
       </c>
       <c r="K18" t="n">
-        <v>2.516945600509644</v>
+        <v>2.485172033309937</v>
       </c>
       <c r="L18" t="n">
-        <v>2.506382179260254</v>
+        <v>2.433553171157837</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.242157220840454</v>
+        <v>2.021843671798706</v>
       </c>
       <c r="C19" t="n">
-        <v>2.329941749572754</v>
+        <v>2.329094648361206</v>
       </c>
       <c r="D19" t="n">
-        <v>2.450610637664795</v>
+        <v>2.161992788314819</v>
       </c>
       <c r="E19" t="n">
-        <v>2.383796215057373</v>
+        <v>2.295652151107788</v>
       </c>
       <c r="F19" t="n">
-        <v>2.280569314956665</v>
+        <v>2.240791082382202</v>
       </c>
       <c r="G19" t="n">
-        <v>2.385280132293701</v>
+        <v>2.252290725708008</v>
       </c>
       <c r="H19" t="n">
-        <v>2.364853143692017</v>
+        <v>2.128072738647461</v>
       </c>
       <c r="I19" t="n">
-        <v>2.132945775985718</v>
+        <v>2.141550302505493</v>
       </c>
       <c r="J19" t="n">
-        <v>2.321458339691162</v>
+        <v>2.191909790039062</v>
       </c>
       <c r="K19" t="n">
-        <v>2.358353614807129</v>
+        <v>2.316614389419556</v>
       </c>
       <c r="L19" t="n">
-        <v>2.324996614456177</v>
+        <v>2.20798122882843</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.220231533050537</v>
+        <v>2.615341186523438</v>
       </c>
       <c r="C20" t="n">
-        <v>2.160378694534302</v>
+        <v>2.16199803352356</v>
       </c>
       <c r="D20" t="n">
-        <v>2.092047929763794</v>
+        <v>2.247776508331299</v>
       </c>
       <c r="E20" t="n">
-        <v>2.166862726211548</v>
+        <v>2.316622495651245</v>
       </c>
       <c r="F20" t="n">
-        <v>2.181326389312744</v>
+        <v>2.221347332000732</v>
       </c>
       <c r="G20" t="n">
-        <v>2.50799560546875</v>
+        <v>2.1664879322052</v>
       </c>
       <c r="H20" t="n">
-        <v>2.539881229400635</v>
+        <v>2.308617353439331</v>
       </c>
       <c r="I20" t="n">
-        <v>2.326446294784546</v>
+        <v>2.161983251571655</v>
       </c>
       <c r="J20" t="n">
-        <v>2.196281433105469</v>
+        <v>2.188422918319702</v>
       </c>
       <c r="K20" t="n">
-        <v>2.104045391082764</v>
+        <v>2.157511711120605</v>
       </c>
       <c r="L20" t="n">
-        <v>2.249549722671509</v>
+        <v>2.254610872268677</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.175825595855713</v>
+        <v>2.196415424346924</v>
       </c>
       <c r="C21" t="n">
-        <v>2.423187971115112</v>
+        <v>2.317600250244141</v>
       </c>
       <c r="D21" t="n">
-        <v>2.216228723526001</v>
+        <v>2.160984754562378</v>
       </c>
       <c r="E21" t="n">
-        <v>2.255136013031006</v>
+        <v>2.1734619140625</v>
       </c>
       <c r="F21" t="n">
-        <v>2.328445434570312</v>
+        <v>2.136067628860474</v>
       </c>
       <c r="G21" t="n">
-        <v>2.429181575775146</v>
+        <v>2.236819267272949</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1788170337677</v>
+        <v>2.254270076751709</v>
       </c>
       <c r="I21" t="n">
-        <v>2.342900276184082</v>
+        <v>2.292664766311646</v>
       </c>
       <c r="J21" t="n">
-        <v>2.259115219116211</v>
+        <v>2.291666746139526</v>
       </c>
       <c r="K21" t="n">
-        <v>2.365856885910034</v>
+        <v>2.070236444473267</v>
       </c>
       <c r="L21" t="n">
-        <v>2.297469472885132</v>
+        <v>2.213018727302551</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.217221021652222</v>
+        <v>2.134068965911865</v>
       </c>
       <c r="C22" t="n">
-        <v>2.278560638427734</v>
+        <v>1.953513622283936</v>
       </c>
       <c r="D22" t="n">
-        <v>2.090066194534302</v>
+        <v>2.120649099349976</v>
       </c>
       <c r="E22" t="n">
-        <v>2.108012676239014</v>
+        <v>1.969480752944946</v>
       </c>
       <c r="F22" t="n">
-        <v>2.337441205978394</v>
+        <v>2.150535821914673</v>
       </c>
       <c r="G22" t="n">
-        <v>2.125958442687988</v>
+        <v>2.068717479705811</v>
       </c>
       <c r="H22" t="n">
-        <v>2.160373449325562</v>
+        <v>2.127592802047729</v>
       </c>
       <c r="I22" t="n">
-        <v>2.03868556022644</v>
+        <v>1.956510066986084</v>
       </c>
       <c r="J22" t="n">
-        <v>2.215169668197632</v>
+        <v>2.075230360031128</v>
       </c>
       <c r="K22" t="n">
-        <v>2.077097415924072</v>
+        <v>1.953534126281738</v>
       </c>
       <c r="L22" t="n">
-        <v>2.164858627319336</v>
+        <v>2.050983309745789</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1.873618364334106</v>
+        <v>1.922120809555054</v>
       </c>
       <c r="C23" t="n">
-        <v>1.900566816329956</v>
+        <v>1.980471611022949</v>
       </c>
       <c r="D23" t="n">
-        <v>2.133950233459473</v>
+        <v>1.9036545753479</v>
       </c>
       <c r="E23" t="n">
-        <v>2.037696123123169</v>
+        <v>1.86873722076416</v>
       </c>
       <c r="F23" t="n">
-        <v>2.103047132492065</v>
+        <v>2.172478675842285</v>
       </c>
       <c r="G23" t="n">
-        <v>2.019737005233765</v>
+        <v>1.88119649887085</v>
       </c>
       <c r="H23" t="n">
-        <v>1.990814685821533</v>
+        <v>1.918126344680786</v>
       </c>
       <c r="I23" t="n">
-        <v>1.872623682022095</v>
+        <v>1.87621283531189</v>
       </c>
       <c r="J23" t="n">
-        <v>1.983839750289917</v>
+        <v>2.090175628662109</v>
       </c>
       <c r="K23" t="n">
-        <v>1.883601903915405</v>
+        <v>1.948051691055298</v>
       </c>
       <c r="L23" t="n">
-        <v>1.979949569702149</v>
+        <v>1.956122589111328</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1.967366456985474</v>
+        <v>2.007888078689575</v>
       </c>
       <c r="C24" t="n">
-        <v>1.94793963432312</v>
+        <v>1.908651828765869</v>
       </c>
       <c r="D24" t="n">
-        <v>1.977849721908569</v>
+        <v>1.991943359375</v>
       </c>
       <c r="E24" t="n">
-        <v>2.127961397171021</v>
+        <v>2.024833679199219</v>
       </c>
       <c r="F24" t="n">
-        <v>2.102024078369141</v>
+        <v>1.996913433074951</v>
       </c>
       <c r="G24" t="n">
-        <v>2.026732683181763</v>
+        <v>2.012872934341431</v>
       </c>
       <c r="H24" t="n">
-        <v>2.139930009841919</v>
+        <v>1.881721973419189</v>
       </c>
       <c r="I24" t="n">
-        <v>2.017743110656738</v>
+        <v>2.094178915023804</v>
       </c>
       <c r="J24" t="n">
-        <v>2.062141895294189</v>
+        <v>1.97546124458313</v>
       </c>
       <c r="K24" t="n">
-        <v>1.923490762710571</v>
+        <v>2.252781391143799</v>
       </c>
       <c r="L24" t="n">
-        <v>2.02931797504425</v>
+        <v>2.014724683761597</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.321475982666016</v>
+        <v>2.053759336471558</v>
       </c>
       <c r="C25" t="n">
-        <v>2.432167768478394</v>
+        <v>2.064269304275513</v>
       </c>
       <c r="D25" t="n">
-        <v>1.986825466156006</v>
+        <v>1.921600103378296</v>
       </c>
       <c r="E25" t="n">
-        <v>2.10601806640625</v>
+        <v>2.230319738388062</v>
       </c>
       <c r="F25" t="n">
-        <v>2.173838138580322</v>
+        <v>1.922115087509155</v>
       </c>
       <c r="G25" t="n">
-        <v>2.114004850387573</v>
+        <v>2.19091010093689</v>
       </c>
       <c r="H25" t="n">
-        <v>2.411939382553101</v>
+        <v>2.109137296676636</v>
       </c>
       <c r="I25" t="n">
-        <v>2.151522159576416</v>
+        <v>2.059267282485962</v>
       </c>
       <c r="J25" t="n">
-        <v>2.07122015953064</v>
+        <v>2.091188430786133</v>
       </c>
       <c r="K25" t="n">
-        <v>2.120103359222412</v>
+        <v>2.330568075180054</v>
       </c>
       <c r="L25" t="n">
-        <v>2.188911533355713</v>
+        <v>2.097313475608826</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.451740980148315</v>
+        <v>2.407869577407837</v>
       </c>
       <c r="C26" t="n">
-        <v>2.583433151245117</v>
+        <v>2.444275856018066</v>
       </c>
       <c r="D26" t="n">
-        <v>2.422838687896729</v>
+        <v>2.34752631187439</v>
       </c>
       <c r="E26" t="n">
-        <v>2.410853385925293</v>
+        <v>2.426814794540405</v>
       </c>
       <c r="F26" t="n">
-        <v>2.358005523681641</v>
+        <v>2.254768133163452</v>
       </c>
       <c r="G26" t="n">
-        <v>2.278687477111816</v>
+        <v>2.367480278015137</v>
       </c>
       <c r="H26" t="n">
-        <v>2.549021482467651</v>
+        <v>2.275723457336426</v>
       </c>
       <c r="I26" t="n">
-        <v>2.321575164794922</v>
+        <v>2.484200954437256</v>
       </c>
       <c r="J26" t="n">
-        <v>2.315608739852905</v>
+        <v>2.558992147445679</v>
       </c>
       <c r="K26" t="n">
-        <v>2.304620981216431</v>
+        <v>2.29664421081543</v>
       </c>
       <c r="L26" t="n">
-        <v>2.399638557434082</v>
+        <v>2.386429572105408</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2.05525803565979</v>
+        <v>2.099157094955444</v>
       </c>
       <c r="C27" t="n">
-        <v>2.196410894393921</v>
+        <v>2.005881547927856</v>
       </c>
       <c r="D27" t="n">
-        <v>2.172463178634644</v>
+        <v>2.353001117706299</v>
       </c>
       <c r="E27" t="n">
-        <v>2.069715976715088</v>
+        <v>2.07271933555603</v>
       </c>
       <c r="F27" t="n">
-        <v>2.164490222930908</v>
+        <v>2.109134912490845</v>
       </c>
       <c r="G27" t="n">
-        <v>2.247274398803711</v>
+        <v>2.184442043304443</v>
       </c>
       <c r="H27" t="n">
-        <v>2.053278684616089</v>
+        <v>2.034330129623413</v>
       </c>
       <c r="I27" t="n">
-        <v>2.361475467681885</v>
+        <v>2.166979789733887</v>
       </c>
       <c r="J27" t="n">
-        <v>2.247791051864624</v>
+        <v>2.150542020797729</v>
       </c>
       <c r="K27" t="n">
-        <v>1.882698059082031</v>
+        <v>2.14503026008606</v>
       </c>
       <c r="L27" t="n">
-        <v>2.145085597038269</v>
+        <v>2.132121825218201</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.125081539154053</v>
+        <v>1.85975980758667</v>
       </c>
       <c r="C28" t="n">
-        <v>2.115097761154175</v>
+        <v>2.155004501342773</v>
       </c>
       <c r="D28" t="n">
-        <v>2.157995462417603</v>
+        <v>1.883708715438843</v>
       </c>
       <c r="E28" t="n">
-        <v>2.272722244262695</v>
+        <v>2.150021314620972</v>
       </c>
       <c r="F28" t="n">
-        <v>2.202447414398193</v>
+        <v>2.081149101257324</v>
       </c>
       <c r="G28" t="n">
-        <v>2.142547607421875</v>
+        <v>2.129957437515259</v>
       </c>
       <c r="H28" t="n">
-        <v>2.085664987564087</v>
+        <v>2.064812183380127</v>
       </c>
       <c r="I28" t="n">
-        <v>2.217360258102417</v>
+        <v>2.252482414245605</v>
       </c>
       <c r="J28" t="n">
-        <v>2.248790264129639</v>
+        <v>2.101644992828369</v>
       </c>
       <c r="K28" t="n">
-        <v>2.201385259628296</v>
+        <v>2.099150896072388</v>
       </c>
       <c r="L28" t="n">
-        <v>2.176909279823303</v>
+        <v>2.077769136428833</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.128073930740356</v>
+        <v>2.101152420043945</v>
       </c>
       <c r="C29" t="n">
-        <v>2.066232442855835</v>
+        <v>1.957011699676514</v>
       </c>
       <c r="D29" t="n">
-        <v>2.072257280349731</v>
+        <v>2.03681206703186</v>
       </c>
       <c r="E29" t="n">
-        <v>2.092685699462891</v>
+        <v>1.996912002563477</v>
       </c>
       <c r="F29" t="n">
-        <v>2.23530101776123</v>
+        <v>2.022841215133667</v>
       </c>
       <c r="G29" t="n">
-        <v>2.19839072227478</v>
+        <v>2.033333778381348</v>
       </c>
       <c r="H29" t="n">
-        <v>2.142032861709595</v>
+        <v>2.127084493637085</v>
       </c>
       <c r="I29" t="n">
-        <v>2.242785930633545</v>
+        <v>2.133071184158325</v>
       </c>
       <c r="J29" t="n">
-        <v>2.081701278686523</v>
+        <v>2.109138250350952</v>
       </c>
       <c r="K29" t="n">
-        <v>2.243797779083252</v>
+        <v>1.934082269668579</v>
       </c>
       <c r="L29" t="n">
-        <v>2.150325894355774</v>
+        <v>2.045143938064575</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.217339992523193</v>
+        <v>2.116129875183105</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180453538894653</v>
+        <v>2.150028705596924</v>
       </c>
       <c r="D30" t="n">
-        <v>2.270204782485962</v>
+        <v>2.41686487197876</v>
       </c>
       <c r="E30" t="n">
-        <v>2.260736703872681</v>
+        <v>2.320106983184814</v>
       </c>
       <c r="F30" t="n">
-        <v>2.159985065460205</v>
+        <v>2.074702262878418</v>
       </c>
       <c r="G30" t="n">
-        <v>2.179460763931274</v>
+        <v>2.094184160232544</v>
       </c>
       <c r="H30" t="n">
-        <v>2.275696516036987</v>
+        <v>2.077213525772095</v>
       </c>
       <c r="I30" t="n">
-        <v>2.163984298706055</v>
+        <v>2.336583614349365</v>
       </c>
       <c r="J30" t="n">
-        <v>2.360989809036255</v>
+        <v>1.9998939037323</v>
       </c>
       <c r="K30" t="n">
-        <v>2.241273403167725</v>
+        <v>2.132061719894409</v>
       </c>
       <c r="L30" t="n">
-        <v>2.231012487411499</v>
+        <v>2.171776962280274</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.856770038604736</v>
+        <v>1.825870275497437</v>
       </c>
       <c r="C31" t="n">
-        <v>1.792458295822144</v>
+        <v>1.797429323196411</v>
       </c>
       <c r="D31" t="n">
-        <v>1.996912956237793</v>
+        <v>1.808423519134521</v>
       </c>
       <c r="E31" t="n">
-        <v>1.810386896133423</v>
+        <v>1.877200365066528</v>
       </c>
       <c r="F31" t="n">
-        <v>1.870227813720703</v>
+        <v>1.826852321624756</v>
       </c>
       <c r="G31" t="n">
-        <v>2.420353651046753</v>
+        <v>1.953533172607422</v>
       </c>
       <c r="H31" t="n">
-        <v>2.242335796356201</v>
+        <v>1.969982624053955</v>
       </c>
       <c r="I31" t="n">
-        <v>1.953524112701416</v>
+        <v>2.057770252227783</v>
       </c>
       <c r="J31" t="n">
-        <v>1.963991641998291</v>
+        <v>1.798416614532471</v>
       </c>
       <c r="K31" t="n">
-        <v>2.016856670379639</v>
+        <v>1.899664402008057</v>
       </c>
       <c r="L31" t="n">
-        <v>1.99238178730011</v>
+        <v>1.881514286994934</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>2.142558336257935</v>
+        <v>1.840815544128418</v>
       </c>
       <c r="C32" t="n">
-        <v>2.075702905654907</v>
+        <v>2.009873867034912</v>
       </c>
       <c r="D32" t="n">
-        <v>2.307611703872681</v>
+        <v>1.87821888923645</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2796950340271</v>
+        <v>1.981983184814453</v>
       </c>
       <c r="F32" t="n">
-        <v>2.319247245788574</v>
+        <v>1.836317300796509</v>
       </c>
       <c r="G32" t="n">
-        <v>2.235185623168945</v>
+        <v>2.042791366577148</v>
       </c>
       <c r="H32" t="n">
-        <v>2.083078384399414</v>
+        <v>1.840299129486084</v>
       </c>
       <c r="I32" t="n">
-        <v>2.036202669143677</v>
+        <v>1.919613599777222</v>
       </c>
       <c r="J32" t="n">
-        <v>2.297527551651001</v>
+        <v>2.290703535079956</v>
       </c>
       <c r="K32" t="n">
-        <v>1.945439577102661</v>
+        <v>2.049313306808472</v>
       </c>
       <c r="L32" t="n">
-        <v>2.172224903106689</v>
+        <v>1.968992972373962</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.377820730209351</v>
+        <v>2.229314804077148</v>
       </c>
       <c r="C33" t="n">
-        <v>2.11099910736084</v>
+        <v>2.243281602859497</v>
       </c>
       <c r="D33" t="n">
-        <v>2.155877590179443</v>
+        <v>2.045307159423828</v>
       </c>
       <c r="E33" t="n">
-        <v>2.405420541763306</v>
+        <v>2.371465921401978</v>
       </c>
       <c r="F33" t="n">
-        <v>2.110009908676147</v>
+        <v>2.138557195663452</v>
       </c>
       <c r="G33" t="n">
-        <v>2.159394979476929</v>
+        <v>2.285760879516602</v>
       </c>
       <c r="H33" t="n">
-        <v>2.195307016372681</v>
+        <v>2.238292217254639</v>
       </c>
       <c r="I33" t="n">
-        <v>2.190295219421387</v>
+        <v>2.14203929901123</v>
       </c>
       <c r="J33" t="n">
-        <v>2.0496506690979</v>
+        <v>2.08519172668457</v>
       </c>
       <c r="K33" t="n">
-        <v>2.15140962600708</v>
+        <v>2.111119270324707</v>
       </c>
       <c r="L33" t="n">
-        <v>2.190618538856506</v>
+        <v>2.189033007621765</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>2.075110912322998</v>
+        <v>1.790439367294312</v>
       </c>
       <c r="C34" t="n">
-        <v>1.951433420181274</v>
+        <v>1.881712913513184</v>
       </c>
       <c r="D34" t="n">
-        <v>1.950925350189209</v>
+        <v>2.254255056381226</v>
       </c>
       <c r="E34" t="n">
-        <v>2.015772104263306</v>
+        <v>1.97499680519104</v>
       </c>
       <c r="F34" t="n">
-        <v>2.149923324584961</v>
+        <v>1.760001420974731</v>
       </c>
       <c r="G34" t="n">
-        <v>2.120995998382568</v>
+        <v>1.82585597038269</v>
       </c>
       <c r="H34" t="n">
-        <v>2.030720472335815</v>
+        <v>2.113128423690796</v>
       </c>
       <c r="I34" t="n">
-        <v>2.009766340255737</v>
+        <v>1.958512783050537</v>
       </c>
       <c r="J34" t="n">
-        <v>2.109997749328613</v>
+        <v>1.906643867492676</v>
       </c>
       <c r="K34" t="n">
-        <v>1.987822294235229</v>
+        <v>2.050302267074585</v>
       </c>
       <c r="L34" t="n">
-        <v>2.040246796607971</v>
+        <v>1.951584887504578</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.617188692092896</v>
+        <v>2.17294979095459</v>
       </c>
       <c r="C35" t="n">
-        <v>2.343403577804565</v>
+        <v>2.208884239196777</v>
       </c>
       <c r="D35" t="n">
-        <v>2.380820035934448</v>
+        <v>2.244296312332153</v>
       </c>
       <c r="E35" t="n">
-        <v>2.425692081451416</v>
+        <v>2.542025566101074</v>
       </c>
       <c r="F35" t="n">
-        <v>2.406749486923218</v>
+        <v>2.332080602645874</v>
       </c>
       <c r="G35" t="n">
-        <v>2.303519010543823</v>
+        <v>2.264227867126465</v>
       </c>
       <c r="H35" t="n">
-        <v>2.441152572631836</v>
+        <v>2.473200798034668</v>
       </c>
       <c r="I35" t="n">
-        <v>2.556853532791138</v>
+        <v>2.237291574478149</v>
       </c>
       <c r="J35" t="n">
-        <v>2.546391487121582</v>
+        <v>2.482203483581543</v>
       </c>
       <c r="K35" t="n">
-        <v>2.407753705978394</v>
+        <v>3.654841899871826</v>
       </c>
       <c r="L35" t="n">
-        <v>2.442952418327331</v>
+        <v>2.461200213432312</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1.865139961242676</v>
+        <v>2.003789663314819</v>
       </c>
       <c r="C36" t="n">
-        <v>2.006780862808228</v>
+        <v>1.96690034866333</v>
       </c>
       <c r="D36" t="n">
-        <v>1.972863912582397</v>
+        <v>1.800317049026489</v>
       </c>
       <c r="E36" t="n">
-        <v>2.119996786117554</v>
+        <v>1.949440956115723</v>
       </c>
       <c r="F36" t="n">
-        <v>2.092055797576904</v>
+        <v>1.839718580245972</v>
       </c>
       <c r="G36" t="n">
-        <v>1.993812561035156</v>
+        <v>1.89606785774231</v>
       </c>
       <c r="H36" t="n">
-        <v>1.990824937820435</v>
+        <v>1.975864410400391</v>
       </c>
       <c r="I36" t="n">
-        <v>2.062628269195557</v>
+        <v>1.985845565795898</v>
       </c>
       <c r="J36" t="n">
-        <v>1.888575792312622</v>
+        <v>1.832231044769287</v>
       </c>
       <c r="K36" t="n">
-        <v>1.922494888305664</v>
+        <v>1.950940847396851</v>
       </c>
       <c r="L36" t="n">
-        <v>1.991517376899719</v>
+        <v>1.920111632347107</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.302517414093018</v>
+        <v>2.192303895950317</v>
       </c>
       <c r="C37" t="n">
-        <v>2.552371740341187</v>
+        <v>2.178826093673706</v>
       </c>
       <c r="D37" t="n">
-        <v>2.284555673599243</v>
+        <v>2.405742168426514</v>
       </c>
       <c r="E37" t="n">
-        <v>2.471565008163452</v>
+        <v>2.235684394836426</v>
       </c>
       <c r="F37" t="n">
-        <v>2.265318393707275</v>
+        <v>2.450634241104126</v>
       </c>
       <c r="G37" t="n">
-        <v>2.411857843399048</v>
+        <v>2.081092834472656</v>
       </c>
       <c r="H37" t="n">
-        <v>2.541017055511475</v>
+        <v>2.386812925338745</v>
       </c>
       <c r="I37" t="n">
-        <v>2.103134632110596</v>
+        <v>2.059641122817993</v>
       </c>
       <c r="J37" t="n">
-        <v>2.490151643753052</v>
+        <v>2.344907522201538</v>
       </c>
       <c r="K37" t="n">
-        <v>2.424827098846436</v>
+        <v>2.35838794708252</v>
       </c>
       <c r="L37" t="n">
-        <v>2.384731650352478</v>
+        <v>2.269403314590454</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.390907287597656</v>
+        <v>2.232689619064331</v>
       </c>
       <c r="C38" t="n">
-        <v>2.72506856918335</v>
+        <v>2.442639350891113</v>
       </c>
       <c r="D38" t="n">
-        <v>2.542021989822388</v>
+        <v>2.534893035888672</v>
       </c>
       <c r="E38" t="n">
-        <v>2.699629068374634</v>
+        <v>2.526941061019897</v>
       </c>
       <c r="F38" t="n">
-        <v>2.359477758407593</v>
+        <v>2.282570838928223</v>
       </c>
       <c r="G38" t="n">
-        <v>2.720071315765381</v>
+        <v>2.441155195236206</v>
       </c>
       <c r="H38" t="n">
-        <v>2.559966802597046</v>
+        <v>2.383291482925415</v>
       </c>
       <c r="I38" t="n">
-        <v>2.662724256515503</v>
+        <v>2.516956567764282</v>
       </c>
       <c r="J38" t="n">
-        <v>2.496128082275391</v>
+        <v>2.397776126861572</v>
       </c>
       <c r="K38" t="n">
-        <v>2.506109237670898</v>
+        <v>2.507978677749634</v>
       </c>
       <c r="L38" t="n">
-        <v>2.566210436820984</v>
+        <v>2.426689195632934</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.120088815689087</v>
+        <v>2.342911243438721</v>
       </c>
       <c r="C39" t="n">
-        <v>2.182456731796265</v>
+        <v>2.186306953430176</v>
       </c>
       <c r="D39" t="n">
-        <v>2.840750217437744</v>
+        <v>2.090575695037842</v>
       </c>
       <c r="E39" t="n">
-        <v>2.402872800827026</v>
+        <v>2.190296411514282</v>
       </c>
       <c r="F39" t="n">
-        <v>2.227323293685913</v>
+        <v>2.336923122406006</v>
       </c>
       <c r="G39" t="n">
-        <v>2.355040788650513</v>
+        <v>2.115985155105591</v>
       </c>
       <c r="H39" t="n">
-        <v>2.244278192520142</v>
+        <v>2.347416162490845</v>
       </c>
       <c r="I39" t="n">
-        <v>2.174490213394165</v>
+        <v>2.101028442382812</v>
       </c>
       <c r="J39" t="n">
-        <v>2.174946308135986</v>
+        <v>2.087088346481323</v>
       </c>
       <c r="K39" t="n">
-        <v>2.366982460021973</v>
+        <v>2.229207754135132</v>
       </c>
       <c r="L39" t="n">
-        <v>2.308922982215881</v>
+        <v>2.202773928642273</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.271712303161621</v>
+        <v>2.029231786727905</v>
       </c>
       <c r="C40" t="n">
-        <v>2.158984899520874</v>
+        <v>2.090065717697144</v>
       </c>
       <c r="D40" t="n">
-        <v>2.194412469863892</v>
+        <v>2.066640615463257</v>
       </c>
       <c r="E40" t="n">
-        <v>2.262741565704346</v>
+        <v>2.103522062301636</v>
       </c>
       <c r="F40" t="n">
-        <v>2.109127521514893</v>
+        <v>2.010867595672607</v>
       </c>
       <c r="G40" t="n">
-        <v>2.403871297836304</v>
+        <v>2.123083829879761</v>
       </c>
       <c r="H40" t="n">
-        <v>2.117108106613159</v>
+        <v>1.993907928466797</v>
       </c>
       <c r="I40" t="n">
-        <v>2.036790609359741</v>
+        <v>2.108132123947144</v>
       </c>
       <c r="J40" t="n">
-        <v>2.154551267623901</v>
+        <v>2.096169948577881</v>
       </c>
       <c r="K40" t="n">
-        <v>2.132059097290039</v>
+        <v>2.020848274230957</v>
       </c>
       <c r="L40" t="n">
-        <v>2.184135913848877</v>
+        <v>2.064246988296509</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.324094772338867</v>
+        <v>2.143548250198364</v>
       </c>
       <c r="C41" t="n">
-        <v>2.407861232757568</v>
+        <v>2.236297369003296</v>
       </c>
       <c r="D41" t="n">
-        <v>2.306638717651367</v>
+        <v>2.325573444366455</v>
       </c>
       <c r="E41" t="n">
-        <v>2.21135950088501</v>
+        <v>2.243792057037354</v>
       </c>
       <c r="F41" t="n">
-        <v>2.565953254699707</v>
+        <v>2.501128196716309</v>
       </c>
       <c r="G41" t="n">
-        <v>2.337048292160034</v>
+        <v>2.523500204086304</v>
       </c>
       <c r="H41" t="n">
-        <v>2.279170513153076</v>
+        <v>2.326462030410767</v>
       </c>
       <c r="I41" t="n">
-        <v>2.301629781723022</v>
+        <v>2.404785394668579</v>
       </c>
       <c r="J41" t="n">
-        <v>2.30662727355957</v>
+        <v>2.412723779678345</v>
       </c>
       <c r="K41" t="n">
-        <v>2.417831182479858</v>
+        <v>2.542389631271362</v>
       </c>
       <c r="L41" t="n">
-        <v>2.345821452140808</v>
+        <v>2.366020035743714</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>2.067224025726318</v>
+        <v>1.912523508071899</v>
       </c>
       <c r="C42" t="n">
-        <v>2.210378408432007</v>
+        <v>2.102028369903564</v>
       </c>
       <c r="D42" t="n">
-        <v>1.996915817260742</v>
+        <v>2.05282735824585</v>
       </c>
       <c r="E42" t="n">
-        <v>2.181450843811035</v>
+        <v>1.998920440673828</v>
       </c>
       <c r="F42" t="n">
-        <v>2.112823963165283</v>
+        <v>2.305634021759033</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12208104133606</v>
+        <v>2.292432546615601</v>
       </c>
       <c r="H42" t="n">
-        <v>1.960007905960083</v>
+        <v>2.071237325668335</v>
       </c>
       <c r="I42" t="n">
-        <v>1.958491802215576</v>
+        <v>2.034812211990356</v>
       </c>
       <c r="J42" t="n">
-        <v>2.046295881271362</v>
+        <v>2.197410345077515</v>
       </c>
       <c r="K42" t="n">
-        <v>1.881188869476318</v>
+        <v>1.921599864959717</v>
       </c>
       <c r="L42" t="n">
-        <v>2.053685855865479</v>
+        <v>2.08894259929657</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.04977011680603</v>
+        <v>2.254760980606079</v>
       </c>
       <c r="C43" t="n">
-        <v>2.318589210510254</v>
+        <v>2.230323791503906</v>
       </c>
       <c r="D43" t="n">
-        <v>2.278695821762085</v>
+        <v>2.077241897583008</v>
       </c>
       <c r="E43" t="n">
-        <v>2.148018836975098</v>
+        <v>2.364468574523926</v>
       </c>
       <c r="F43" t="n">
-        <v>2.425325870513916</v>
+        <v>2.309613943099976</v>
       </c>
       <c r="G43" t="n">
-        <v>2.10412859916687</v>
+        <v>2.3185875415802</v>
       </c>
       <c r="H43" t="n">
-        <v>2.10413122177124</v>
+        <v>2.253773927688599</v>
       </c>
       <c r="I43" t="n">
-        <v>2.252264976501465</v>
+        <v>2.251263856887817</v>
       </c>
       <c r="J43" t="n">
-        <v>2.118101119995117</v>
+        <v>2.252768278121948</v>
       </c>
       <c r="K43" t="n">
-        <v>2.046298027038574</v>
+        <v>2.234292268753052</v>
       </c>
       <c r="L43" t="n">
-        <v>2.184532380104065</v>
+        <v>2.254709506034851</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.193408012390137</v>
+        <v>2.252779483795166</v>
       </c>
       <c r="C44" t="n">
-        <v>2.08219838142395</v>
+        <v>2.25825834274292</v>
       </c>
       <c r="D44" t="n">
-        <v>2.17095947265625</v>
+        <v>2.195423364639282</v>
       </c>
       <c r="E44" t="n">
-        <v>2.062238693237305</v>
+        <v>1.903645753860474</v>
       </c>
       <c r="F44" t="n">
-        <v>2.045777082443237</v>
+        <v>2.079207897186279</v>
       </c>
       <c r="G44" t="n">
-        <v>2.16648268699646</v>
+        <v>2.185446262359619</v>
       </c>
       <c r="H44" t="n">
-        <v>2.094162225723267</v>
+        <v>2.022847175598145</v>
       </c>
       <c r="I44" t="n">
-        <v>2.348511934280396</v>
+        <v>1.929569482803345</v>
       </c>
       <c r="J44" t="n">
-        <v>2.076205492019653</v>
+        <v>2.092174530029297</v>
       </c>
       <c r="K44" t="n">
-        <v>2.117110252380371</v>
+        <v>2.039793014526367</v>
       </c>
       <c r="L44" t="n">
-        <v>2.135705423355103</v>
+        <v>2.095914530754089</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>2.189418792724609</v>
+        <v>2.18044900894165</v>
       </c>
       <c r="C45" t="n">
-        <v>2.008883237838745</v>
+        <v>1.955025911331177</v>
       </c>
       <c r="D45" t="n">
-        <v>1.987939834594727</v>
+        <v>2.076700210571289</v>
       </c>
       <c r="E45" t="n">
-        <v>1.926584243774414</v>
+        <v>2.000900268554688</v>
       </c>
       <c r="F45" t="n">
-        <v>2.049268484115601</v>
+        <v>2.033326387405396</v>
       </c>
       <c r="G45" t="n">
-        <v>1.890676259994507</v>
+        <v>2.141185522079468</v>
       </c>
       <c r="H45" t="n">
-        <v>1.916617155075073</v>
+        <v>1.964999437332153</v>
       </c>
       <c r="I45" t="n">
-        <v>1.937561511993408</v>
+        <v>1.938560009002686</v>
       </c>
       <c r="J45" t="n">
-        <v>2.121094465255737</v>
+        <v>1.835367918014526</v>
       </c>
       <c r="K45" t="n">
-        <v>2.220851898193359</v>
+        <v>1.979847192764282</v>
       </c>
       <c r="L45" t="n">
-        <v>2.024889588356018</v>
+        <v>2.010636186599732</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1.946045637130737</v>
+        <v>1.763897895812988</v>
       </c>
       <c r="C46" t="n">
-        <v>1.893696069717407</v>
+        <v>2.024251222610474</v>
       </c>
       <c r="D46" t="n">
-        <v>1.931575059890747</v>
+        <v>1.685635089874268</v>
       </c>
       <c r="E46" t="n">
-        <v>1.766500949859619</v>
+        <v>1.767401456832886</v>
       </c>
       <c r="F46" t="n">
-        <v>1.87919282913208</v>
+        <v>1.817268371582031</v>
       </c>
       <c r="G46" t="n">
-        <v>1.98893141746521</v>
+        <v>1.905534744262695</v>
       </c>
       <c r="H46" t="n">
-        <v>2.144545316696167</v>
+        <v>1.952020168304443</v>
       </c>
       <c r="I46" t="n">
-        <v>2.008875131607056</v>
+        <v>1.880101203918457</v>
       </c>
       <c r="J46" t="n">
-        <v>2.080686807632446</v>
+        <v>1.950386047363281</v>
       </c>
       <c r="K46" t="n">
-        <v>1.948039293289185</v>
+        <v>2.001577615737915</v>
       </c>
       <c r="L46" t="n">
-        <v>1.958808851242065</v>
+        <v>1.874807381629944</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.899110555648804</v>
+        <v>2.728487730026245</v>
       </c>
       <c r="C47" t="n">
-        <v>2.532038927078247</v>
+        <v>2.887166261672974</v>
       </c>
       <c r="D47" t="n">
-        <v>2.482169628143311</v>
+        <v>2.553003072738647</v>
       </c>
       <c r="E47" t="n">
-        <v>2.541033267974854</v>
+        <v>2.473190784454346</v>
       </c>
       <c r="F47" t="n">
-        <v>2.721556425094604</v>
+        <v>2.715570449829102</v>
       </c>
       <c r="G47" t="n">
-        <v>2.800886392593384</v>
+        <v>2.540541887283325</v>
       </c>
       <c r="H47" t="n">
-        <v>2.956483602523804</v>
+        <v>2.541017293930054</v>
       </c>
       <c r="I47" t="n">
-        <v>2.624188661575317</v>
+        <v>2.527058839797974</v>
       </c>
       <c r="J47" t="n">
-        <v>2.948832511901855</v>
+        <v>2.659726619720459</v>
       </c>
       <c r="K47" t="n">
-        <v>2.636649608612061</v>
+        <v>2.700629234313965</v>
       </c>
       <c r="L47" t="n">
-        <v>2.714294958114624</v>
+        <v>2.632639217376709</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.229190826416016</v>
+        <v>2.201395273208618</v>
       </c>
       <c r="C48" t="n">
-        <v>2.531899452209473</v>
+        <v>2.118122577667236</v>
       </c>
       <c r="D48" t="n">
-        <v>2.376811981201172</v>
+        <v>2.388925313949585</v>
       </c>
       <c r="E48" t="n">
-        <v>2.325448989868164</v>
+        <v>2.246272563934326</v>
       </c>
       <c r="F48" t="n">
-        <v>2.191300868988037</v>
+        <v>2.196413516998291</v>
       </c>
       <c r="G48" t="n">
-        <v>2.258622884750366</v>
+        <v>2.35053277015686</v>
       </c>
       <c r="H48" t="n">
-        <v>2.316462278366089</v>
+        <v>2.020359516143799</v>
       </c>
       <c r="I48" t="n">
-        <v>2.129948377609253</v>
+        <v>2.128075122833252</v>
       </c>
       <c r="J48" t="n">
-        <v>2.608215570449829</v>
+        <v>2.339555978775024</v>
       </c>
       <c r="K48" t="n">
-        <v>2.291533470153809</v>
+        <v>2.274726867675781</v>
       </c>
       <c r="L48" t="n">
-        <v>2.325943470001221</v>
+        <v>2.226437950134277</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.348887205123901</v>
+        <v>2.193410873413086</v>
       </c>
       <c r="C49" t="n">
-        <v>2.387789487838745</v>
+        <v>2.125080108642578</v>
       </c>
       <c r="D49" t="n">
-        <v>2.281057357788086</v>
+        <v>2.201388359069824</v>
       </c>
       <c r="E49" t="n">
-        <v>2.401745796203613</v>
+        <v>2.147025346755981</v>
       </c>
       <c r="F49" t="n">
-        <v>2.325442790985107</v>
+        <v>2.301636457443237</v>
       </c>
       <c r="G49" t="n">
-        <v>2.367834806442261</v>
+        <v>2.154505491256714</v>
       </c>
       <c r="H49" t="n">
-        <v>2.415714502334595</v>
+        <v>2.193416595458984</v>
       </c>
       <c r="I49" t="n">
-        <v>2.361912250518799</v>
+        <v>2.214372873306274</v>
       </c>
       <c r="J49" t="n">
-        <v>2.430688381195068</v>
+        <v>2.446770429611206</v>
       </c>
       <c r="K49" t="n">
-        <v>2.399884939193726</v>
+        <v>2.245783090591431</v>
       </c>
       <c r="L49" t="n">
-        <v>2.37209575176239</v>
+        <v>2.222338962554931</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.039793014526367</v>
+        <v>1.863245248794556</v>
       </c>
       <c r="C50" t="n">
-        <v>2.04828667640686</v>
+        <v>2.03733491897583</v>
       </c>
       <c r="D50" t="n">
-        <v>2.198423862457275</v>
+        <v>1.952514886856079</v>
       </c>
       <c r="E50" t="n">
-        <v>2.310600519180298</v>
+        <v>2.075244903564453</v>
       </c>
       <c r="F50" t="n">
-        <v>2.219352245330811</v>
+        <v>2.028823375701904</v>
       </c>
       <c r="G50" t="n">
-        <v>2.19839334487915</v>
+        <v>2.19441819190979</v>
       </c>
       <c r="H50" t="n">
-        <v>2.112122058868408</v>
+        <v>1.990953207015991</v>
       </c>
       <c r="I50" t="n">
-        <v>2.057275056838989</v>
+        <v>2.212372779846191</v>
       </c>
       <c r="J50" t="n">
-        <v>2.155985116958618</v>
+        <v>2.136065244674683</v>
       </c>
       <c r="K50" t="n">
-        <v>2.086176156997681</v>
+        <v>2.23084831237793</v>
       </c>
       <c r="L50" t="n">
-        <v>2.142640805244446</v>
+        <v>2.072182106971741</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1.976957321166992</v>
+        <v>2.353517770767212</v>
       </c>
       <c r="C51" t="n">
-        <v>2.022843837738037</v>
+        <v>2.457288026809692</v>
       </c>
       <c r="D51" t="n">
-        <v>2.193416357040405</v>
+        <v>2.246386289596558</v>
       </c>
       <c r="E51" t="n">
-        <v>2.103162050247192</v>
+        <v>2.08120059967041</v>
       </c>
       <c r="F51" t="n">
-        <v>2.272197008132935</v>
+        <v>2.022860050201416</v>
       </c>
       <c r="G51" t="n">
-        <v>2.193910598754883</v>
+        <v>2.395947694778442</v>
       </c>
       <c r="H51" t="n">
-        <v>2.088199377059937</v>
+        <v>2.107136726379395</v>
       </c>
       <c r="I51" t="n">
-        <v>2.026848316192627</v>
+        <v>2.377195119857788</v>
       </c>
       <c r="J51" t="n">
-        <v>2.058256864547729</v>
+        <v>2.082592248916626</v>
       </c>
       <c r="K51" t="n">
-        <v>1.935558795928955</v>
+        <v>2.428231000900269</v>
       </c>
       <c r="L51" t="n">
-        <v>2.087135052680969</v>
+        <v>2.255235552787781</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.244870181083679</v>
+        <v>2.135807294845581</v>
       </c>
       <c r="C52" t="n">
-        <v>2.256657795906067</v>
+        <v>2.189068322181702</v>
       </c>
       <c r="D52" t="n">
-        <v>2.24311514377594</v>
+        <v>2.183934011459351</v>
       </c>
       <c r="E52" t="n">
-        <v>2.238842744827271</v>
+        <v>2.220959358215332</v>
       </c>
       <c r="F52" t="n">
-        <v>2.270753169059753</v>
+        <v>2.174462332725525</v>
       </c>
       <c r="G52" t="n">
-        <v>2.300784034729004</v>
+        <v>2.194674873352051</v>
       </c>
       <c r="H52" t="n">
-        <v>2.271188702583313</v>
+        <v>2.192398743629456</v>
       </c>
       <c r="I52" t="n">
-        <v>2.252790818214416</v>
+        <v>2.187174949645996</v>
       </c>
       <c r="J52" t="n">
-        <v>2.279181203842163</v>
+        <v>2.199853415489197</v>
       </c>
       <c r="K52" t="n">
-        <v>2.212693328857422</v>
+        <v>2.218798694610596</v>
       </c>
       <c r="L52" t="n">
-        <v>2.257087712287903</v>
+        <v>2.189713199615478</v>
       </c>
     </row>
   </sheetData>
